--- a/better_data_1.xlsx
+++ b/better_data_1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -52,11 +52,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,10 +67,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,7 +86,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -91,35 +96,76 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="12">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -128,10 +174,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -169,69 +215,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -255,54 +303,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -312,7 +359,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -321,7 +368,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -330,7 +377,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -338,10 +385,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -370,7 +417,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -383,13 +430,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -407,6131 +453,6148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:K175"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4">
         <v>45675</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>2210</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="5">
         <v>1646</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="5">
         <v>1098</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5">
         <v>192</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="5">
         <v>5072</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
         <v>13.4</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
         <v>2.7</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="5">
         <v>4982</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="4">
         <v>45676</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>2134</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="5">
         <v>1584</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="5">
         <v>1104</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="5">
         <v>150</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="5">
         <v>4982</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
         <v>16.9</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
         <v>3.2</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>4831</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="4">
         <v>45677</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>2090</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <v>1543</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="5">
         <v>1018</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <v>223</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="5">
         <v>4831</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
         <v>16.6</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K4">
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>9.2</v>
+      </c>
+      <c r="K4" s="5">
         <v>4755</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="2">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="4">
         <v>45678</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>1980</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="5">
         <v>1644</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="5">
         <v>995</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="5">
         <v>221</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="5">
         <v>4755</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>16</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
         <v>10.2</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>4829</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="2">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="4">
         <v>45679</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>2020</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="5">
         <v>1574</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="5">
         <v>1035</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="5">
         <v>218</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5">
         <v>4829</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
         <v>16.1</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
         <v>5.7</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>4548</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="2">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="4">
         <v>45680</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>2102</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="5">
         <v>1473</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="5">
         <v>967</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="5">
         <v>166</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="5">
         <v>4548</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
         <v>16.8</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
         <v>8.9</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>4840</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="2">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4">
         <v>45681</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>2059</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="5">
         <v>1570</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="5">
         <v>1015</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="5">
         <v>192</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="5">
         <v>4840</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
         <v>15.6</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
         <v>10.2</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>4560</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="2">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="4">
         <v>45682</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>2006</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>1396</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="5">
         <v>970</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="5">
         <v>175</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="5">
         <v>4560</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
         <v>14.7</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
         <v>9.4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>4055</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="2">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="4">
         <v>45683</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="5">
         <v>1914</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="5">
         <v>1128</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="5">
         <v>881</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="5">
         <v>133</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="5">
         <v>4055</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="5">
         <v>1</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="6">
         <v>14.5</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
         <v>6.1</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="5">
         <v>4599</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="2">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="4">
         <v>45684</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="5">
         <v>2035</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="5">
         <v>1454</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="5">
         <v>928</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="5">
         <v>186</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="5">
         <v>4599</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
         <v>14.4</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
         <v>6.6</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="5">
         <v>4674</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="2">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="4">
         <v>45685</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="5">
         <v>2014</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="5">
         <v>1518</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="5">
         <v>932</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="5">
         <v>181</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="5">
         <v>4674</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
         <v>14.8</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
         <v>4.3</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="5">
         <v>4708</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="2">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="4">
         <v>45686</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="5">
         <v>2078</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="5">
         <v>1490</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="5">
         <v>977</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="5">
         <v>191</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="5">
         <v>4708</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
         <v>16.2</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
         <v>7.7</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="5">
         <v>4599</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="2">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="4">
         <v>45687</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="5">
         <v>2010</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="5">
         <v>1486</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="5">
         <v>918</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="5">
         <v>182</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="5">
         <v>4599</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
         <v>17.6</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
         <v>7.6</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="5">
         <v>4434</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="2">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="4">
         <v>45689</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="5">
         <v>1951</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="5">
         <v>1366</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="5">
         <v>956</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="5">
         <v>160</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="5">
         <v>4434</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
         <v>16.6</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="6">
         <v>0.1</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="6">
         <v>4.5</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="5">
         <v>4629</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="2">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="4">
         <v>45690</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="5">
         <v>1984</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="5">
         <v>1505</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="5">
         <v>1008</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="5">
         <v>137</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="5">
         <v>4629</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
         <v>15.4</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K16">
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>9.8</v>
+      </c>
+      <c r="K16" s="5">
         <v>4588</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="2">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="4">
         <v>45691</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="5">
         <v>1964</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="5">
         <v>1530</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="5">
         <v>966</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="5">
         <v>185</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="5">
         <v>4588</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
         <v>15.3</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
         <v>6.8</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="5">
         <v>4531</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="2">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="4">
         <v>45692</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="5">
         <v>1954</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="5">
         <v>1498</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="5">
         <v>925</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="5">
         <v>300</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="5">
         <v>4531</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
         <v>18.2</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
         <v>4.8</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="5">
         <v>4058</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="2">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="4">
         <v>45693</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="5">
         <v>1812</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="5">
         <v>1237</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="5">
         <v>861</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="5">
         <v>139</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="5">
         <v>4058</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="5">
         <v>1</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="6">
         <v>15.7</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
         <v>10</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="5">
         <v>4328</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="2">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="4">
         <v>45694</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="5">
         <v>1844</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="5">
         <v>1416</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="5">
         <v>904</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="5">
         <v>180</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="5">
         <v>4328</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
         <v>16.3</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
         <v>12.1</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="5">
         <v>4411</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="2">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="4">
         <v>45696</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="5">
         <v>1921</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="5">
         <v>1369</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="5">
         <v>962</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="5">
         <v>140</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="5">
         <v>4411</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
         <v>16.2</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6">
         <v>9.9</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="5">
         <v>4332</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="2">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="4">
         <v>45697</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="5">
         <v>1826</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="5">
         <v>1413</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="5">
         <v>936</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="5">
         <v>131</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="5">
         <v>4332</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6">
         <v>17.2</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="6">
         <v>4.3</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="5">
         <v>4311</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="2">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="4">
         <v>45698</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="5">
         <v>1863</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="5">
         <v>1399</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="5">
         <v>899</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="5">
         <v>156</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="5">
         <v>4311</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6">
         <v>18.4</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6">
         <v>3.5</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="5">
         <v>4237</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="2">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="4">
         <v>45699</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="5">
         <v>1845</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="5">
         <v>1395</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="5">
         <v>869</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="5">
         <v>144</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="5">
         <v>4237</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
         <v>19.5</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6">
         <v>3.8</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="5">
         <v>4548</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="2">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="4">
         <v>45700</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="5">
         <v>1919</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="5">
         <v>1475</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="5">
         <v>984</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="5">
         <v>142</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="5">
         <v>4548</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="5">
         <v>1</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="6">
         <v>18.4</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
+      <c r="I25" s="5">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6">
         <v>11.8</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="5">
         <v>4254</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="2">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="4">
         <v>45701</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="5">
         <v>1786</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="5">
         <v>1402</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="5">
         <v>939</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="5">
         <v>143</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="5">
         <v>4254</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
         <v>17.6</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
+      <c r="I26" s="5">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6">
         <v>15.1</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="5">
         <v>4258</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="2">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="4">
         <v>45702</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="5">
         <v>1834</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="5">
         <v>1420</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="5">
         <v>887</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="5">
         <v>149</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="5">
         <v>4258</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
         <v>17.4</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
+      <c r="I27" s="5">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5">
         <v>12</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="5">
         <v>4130</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="2">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="4">
         <v>45703</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="5">
         <v>1812</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="5">
         <v>1281</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="5">
         <v>947</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="5">
         <v>122</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="5">
         <v>4130</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
+      <c r="G28" s="5">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6">
         <v>18.9</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
+      <c r="I28" s="5">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6">
         <v>5.1</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="5">
         <v>4144</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="2">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="4">
         <v>45704</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="5">
         <v>1777</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="5">
         <v>1339</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="5">
         <v>908</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="5">
         <v>116</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="5">
         <v>4144</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
+      <c r="G29" s="5">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6">
         <v>19.9</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
+      <c r="I29" s="5">
+        <v>0</v>
+      </c>
+      <c r="J29" s="6">
         <v>4.2</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="5">
         <v>4111</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="2">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="4">
         <v>45705</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="5">
         <v>1762</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="5">
         <v>1385</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="5">
         <v>871</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="5">
         <v>139</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="5">
         <v>4111</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
+      <c r="G30" s="5">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6">
         <v>20.2</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
+      <c r="I30" s="5">
+        <v>0</v>
+      </c>
+      <c r="J30" s="6">
         <v>3.1</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="5">
         <v>4153</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="2">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="4">
         <v>45706</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="5">
         <v>1711</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="5">
         <v>1437</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="5">
         <v>898</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="5">
         <v>150</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="5">
         <v>4153</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
+      <c r="G31" s="5">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6">
         <v>20.5</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
+      <c r="I31" s="5">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5">
         <v>6</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="5">
         <v>4187</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="2">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="4">
         <v>45707</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="5">
         <v>1750</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="5">
         <v>1391</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="5">
         <v>909</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="5">
         <v>159</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="5">
         <v>4187</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
+      <c r="G32" s="5">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5">
         <v>20</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="6">
         <v>2.2</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="6">
         <v>6.1</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="5">
         <v>4152</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="2">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="4">
         <v>45708</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="5">
         <v>1718</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="5">
         <v>1388</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="5">
         <v>893</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="5">
         <v>170</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="5">
         <v>4152</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6">
         <v>20.3</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="5">
         <v>1</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="6">
         <v>12.8</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="5">
         <v>4245</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="2">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="4">
         <v>45709</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="5">
         <v>1764</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="5">
         <v>1412</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="5">
         <v>937</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="5">
         <v>173</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="5">
         <v>4245</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
+      <c r="G34" s="5">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6">
         <v>18.8</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
+      <c r="I34" s="5">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6">
         <v>8.5</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="5">
         <v>3958</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="2">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="4">
         <v>45710</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="5">
         <v>1744</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="5">
         <v>1220</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="5">
         <v>873</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="5">
         <v>131</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="5">
         <v>3958</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
+      <c r="G35" s="5">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6">
         <v>17.4</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
+      <c r="I35" s="5">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6">
         <v>10.5</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="5">
         <v>4046</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="2">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="4">
         <v>45711</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="5">
         <v>1684</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="5">
         <v>1318</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="5">
         <v>884</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="5">
         <v>130</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="5">
         <v>4046</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
+      <c r="G36" s="5">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6">
         <v>18.5</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
+      <c r="I36" s="5">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6">
         <v>7.2</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="5">
         <v>4059</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="2">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="4">
         <v>45712</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="5">
         <v>1738</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="5">
         <v>1358</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="5">
         <v>856</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="5">
         <v>155</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="5">
         <v>4059</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
+      <c r="G37" s="5">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6">
         <v>19.2</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
+      <c r="I37" s="5">
+        <v>0</v>
+      </c>
+      <c r="J37" s="6">
         <v>6.1</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="5">
         <v>4110</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="2">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="4">
         <v>45713</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="5">
         <v>1729</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="5">
         <v>1379</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="5">
         <v>857</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="5">
         <v>153</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="5">
         <v>4110</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
+      <c r="G38" s="5">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6">
         <v>20.2</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
+      <c r="I38" s="5">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6">
         <v>3.9</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="5">
         <v>4323</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="2">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="4">
         <v>45714</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="5">
         <v>1859</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="5">
         <v>1459</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="5">
         <v>929</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="5">
         <v>199</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="5">
         <v>4323</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="5">
         <v>1</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="6">
         <v>23.7</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
+      <c r="I39" s="5">
+        <v>0</v>
+      </c>
+      <c r="J39" s="6">
         <v>5.1</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="5">
         <v>3971</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="2">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="4">
         <v>45715</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="5">
         <v>1640</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="5">
         <v>1310</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="5">
         <v>848</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="5">
         <v>178</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="5">
         <v>3971</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
+      <c r="G40" s="5">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6">
         <v>21.6</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
+      <c r="I40" s="5">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5">
         <v>10</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="5">
         <v>4348</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="2">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="4">
         <v>45716</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="5">
         <v>1922</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="5">
         <v>1543</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="5">
         <v>1067</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="5">
         <v>251</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="5">
         <v>4348</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
+      <c r="G41" s="5">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6">
         <v>21.4</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="6">
         <v>20.1</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="6">
         <v>11.3</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="5">
         <v>3904</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="2">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="4">
         <v>45717</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="5">
         <v>1686</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="5">
         <v>1264</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="5">
         <v>882</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="5">
         <v>159</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="5">
         <v>3904</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
+      <c r="G42" s="5">
+        <v>0</v>
+      </c>
+      <c r="H42" s="6">
         <v>21.2</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="5">
         <v>1</v>
       </c>
-      <c r="J42">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K42">
+      <c r="J42" s="6">
+        <v>8.7</v>
+      </c>
+      <c r="K42" s="5">
         <v>3841</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="2">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+      <c r="A43" s="4">
         <v>45718</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="5">
         <v>1549</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="5">
         <v>1288</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="5">
         <v>847</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="5">
         <v>123</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="5">
         <v>3841</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
+      <c r="G43" s="5">
+        <v>0</v>
+      </c>
+      <c r="H43" s="6">
         <v>19.9</v>
       </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="K43">
+      <c r="I43" s="5">
+        <v>0</v>
+      </c>
+      <c r="J43" s="6">
+        <v>9.3</v>
+      </c>
+      <c r="K43" s="5">
         <v>3913</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="2">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+      <c r="A44" s="4">
         <v>45719</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="5">
         <v>1674</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="5">
         <v>1345</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="5">
         <v>830</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="5">
         <v>155</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="5">
         <v>3913</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
+      <c r="G44" s="5">
+        <v>0</v>
+      </c>
+      <c r="H44" s="6">
         <v>21.2</v>
       </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
+      <c r="I44" s="5">
+        <v>0</v>
+      </c>
+      <c r="J44" s="6">
         <v>6.5</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="5">
         <v>3939</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="2">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+      <c r="A45" s="4">
         <v>45720</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="5">
         <v>1639</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="5">
         <v>1365</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="5">
         <v>804</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="5">
         <v>192</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="5">
         <v>3939</v>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
+      <c r="G45" s="5">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5">
         <v>21</v>
       </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
+      <c r="I45" s="5">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5">
         <v>14</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="5">
         <v>4073</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="2">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+      <c r="A46" s="4">
         <v>45721</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="5">
         <v>1684</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="5">
         <v>1370</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="5">
         <v>934</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="5">
         <v>153</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="5">
         <v>4073</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
+      <c r="G46" s="5">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6">
         <v>17.3</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
+      <c r="I46" s="5">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5">
         <v>18</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="5">
         <v>4000</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="2">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+      <c r="A47" s="4">
         <v>45722</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="5">
         <v>1616</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="5">
         <v>1378</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="5">
         <v>901</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="5">
         <v>148</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="5">
         <v>4000</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
+      <c r="G47" s="5">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6">
         <v>18.7</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
+      <c r="I47" s="5">
+        <v>0</v>
+      </c>
+      <c r="J47" s="6">
         <v>11.8</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="5">
         <v>4219</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="2">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+      <c r="A48" s="4">
         <v>45723</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="5">
         <v>1720</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="5">
         <v>1483</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="5">
         <v>960</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="5">
         <v>178</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="5">
         <v>4219</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
+      <c r="G48" s="5">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6">
         <v>20.1</v>
       </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
+      <c r="I48" s="5">
+        <v>0</v>
+      </c>
+      <c r="J48" s="6">
         <v>7.3</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="5">
         <v>3842</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="2">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+      <c r="A49" s="4">
         <v>45724</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="5">
         <v>1650</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="5">
         <v>1231</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="5">
         <v>855</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="5">
         <v>134</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="5">
         <v>3842</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
+      <c r="G49" s="5">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6">
         <v>21.8</v>
       </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
+      <c r="I49" s="5">
+        <v>0</v>
+      </c>
+      <c r="J49" s="6">
         <v>7.9</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="5">
         <v>3796</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="2">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+      <c r="A50" s="4">
         <v>45725</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="5">
         <v>1564</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="5">
         <v>1441</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="5">
         <v>876</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="5">
         <v>209</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="5">
         <v>3796</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
+      <c r="G50" s="5">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6">
         <v>24.2</v>
       </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
+      <c r="I50" s="5">
+        <v>0</v>
+      </c>
+      <c r="J50" s="6">
         <v>7.3</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="5">
         <v>3968</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="2">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+      <c r="A51" s="4">
         <v>45726</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="5">
         <v>1652</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="5">
         <v>1336</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="5">
         <v>818</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="5">
         <v>198</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="5">
         <v>3968</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
+      <c r="G51" s="5">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6">
         <v>24.8</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
+      <c r="I51" s="5">
+        <v>0</v>
+      </c>
+      <c r="J51" s="6">
         <v>10.4</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="5">
         <v>3998</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="2">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+      <c r="A52" s="4">
         <v>45727</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="5">
         <v>1650</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="5">
         <v>1390</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="5">
         <v>923</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="5">
         <v>297</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="5">
         <v>3998</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
+      <c r="G52" s="5">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6">
         <v>25.9</v>
       </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
+      <c r="I52" s="5">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5">
         <v>6</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="5">
         <v>4012</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="2">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+      <c r="A53" s="4">
         <v>45728</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="5">
         <v>1665</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="5">
         <v>1336</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="5">
         <v>858</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="5">
         <v>204</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="5">
         <v>4012</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
+      <c r="G53" s="5">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6">
         <v>24.5</v>
       </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K53">
+      <c r="I53" s="5">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6">
+        <v>9.2</v>
+      </c>
+      <c r="K53" s="5">
         <v>4030</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="2">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+      <c r="A54" s="4">
         <v>45729</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="5">
         <v>1675</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="5">
         <v>1332</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="5">
         <v>887</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="5">
         <v>196</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="5">
         <v>4030</v>
       </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
+      <c r="G54" s="5">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6">
         <v>25.4</v>
       </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
+      <c r="I54" s="5">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6">
         <v>6.9</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="5">
         <v>3919</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="2">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+      <c r="A55" s="4">
         <v>45731</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="5">
         <v>1488</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="5">
         <v>962</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="5">
         <v>776</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="5">
         <v>142</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="5">
         <v>3919</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
+      <c r="G55" s="5">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6">
         <v>24.5</v>
       </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
+      <c r="I55" s="5">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6">
         <v>12.1</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="5">
         <v>3486</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="2">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+      <c r="A56" s="4">
         <v>45732</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="5">
         <v>1451</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="5">
         <v>1148</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="5">
         <v>772</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="5">
         <v>130</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="5">
         <v>3486</v>
       </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
+      <c r="G56" s="5">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6">
         <v>23.8</v>
       </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
+      <c r="I56" s="5">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6">
         <v>10.1</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="5">
         <v>3775</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
-      <c r="A57" s="2">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+      <c r="A57" s="4">
         <v>45733</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="5">
         <v>1587</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="5">
         <v>1266</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="5">
         <v>813</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="5">
         <v>174</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="5">
         <v>3775</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
+      <c r="G57" s="5">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6">
         <v>22.9</v>
       </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
+      <c r="I57" s="5">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6">
         <v>10.6</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="5">
         <v>3871</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
-      <c r="A58" s="2">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+      <c r="A58" s="4">
         <v>45734</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="5">
         <v>1634</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="5">
         <v>1315</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="5">
         <v>826</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="5">
         <v>154</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="5">
         <v>3871</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
+      <c r="G58" s="5">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6">
         <v>22.8</v>
       </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
+      <c r="I58" s="5">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
         <v>9.4</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="5">
         <v>3952</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
-      <c r="A59" s="2">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+      <c r="A59" s="4">
         <v>45735</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="5">
         <v>1640</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="5">
         <v>1333</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="5">
         <v>865</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="5">
         <v>166</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="5">
         <v>3952</v>
       </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
+      <c r="G59" s="5">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6">
         <v>24.1</v>
       </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
+      <c r="I59" s="5">
+        <v>0</v>
+      </c>
+      <c r="J59" s="6">
         <v>7.6</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="5">
         <v>4022</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
-      <c r="A60" s="2">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+      <c r="A60" s="4">
         <v>45736</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="5">
         <v>1639</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="5">
         <v>1334</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="5">
         <v>885</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="5">
         <v>181</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="5">
         <v>4022</v>
       </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
+      <c r="G60" s="5">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6">
         <v>25.5</v>
       </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
+      <c r="I60" s="5">
+        <v>0</v>
+      </c>
+      <c r="J60" s="6">
         <v>7.2</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="5">
         <v>4104</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
-      <c r="A61" s="2">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+      <c r="A61" s="4">
         <v>45737</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="5">
         <v>1661</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="5">
         <v>1376</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="5">
         <v>897</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="5">
         <v>217</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="5">
         <v>4104</v>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
+      <c r="G61" s="5">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6">
         <v>24.1</v>
       </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
+      <c r="I61" s="5">
+        <v>0</v>
+      </c>
+      <c r="J61" s="6">
         <v>9.9</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="5">
         <v>3785</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
-      <c r="A62" s="2">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+      <c r="A62" s="4">
         <v>45738</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="5">
         <v>1621</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="5">
         <v>1186</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="5">
         <v>879</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="5">
         <v>146</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="5">
         <v>3785</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
+      <c r="G62" s="5">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6">
         <v>24.6</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="6">
         <v>0.1</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="6">
         <v>7.2</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="5">
         <v>3683</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="2">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+      <c r="A63" s="4">
         <v>45739</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="5">
         <v>1527</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="5">
         <v>1243</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="5">
         <v>830</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="5">
         <v>159</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="5">
         <v>3683</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
+      <c r="G63" s="5">
+        <v>0</v>
+      </c>
+      <c r="H63" s="6">
         <v>25.7</v>
       </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
+      <c r="I63" s="5">
+        <v>0</v>
+      </c>
+      <c r="J63" s="6">
         <v>6.2</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="5">
         <v>4070</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="2">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+      <c r="A64" s="4">
         <v>45740</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="5">
         <v>1679</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="5">
         <v>1366</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="5">
         <v>885</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="5">
         <v>220</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="5">
         <v>4070</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
+      <c r="G64" s="5">
+        <v>0</v>
+      </c>
+      <c r="H64" s="6">
         <v>26.6</v>
       </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
+      <c r="I64" s="5">
+        <v>0</v>
+      </c>
+      <c r="J64" s="6">
         <v>5.8</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="5">
         <v>4099</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
-      <c r="A65" s="2">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+      <c r="A65" s="4">
         <v>45741</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="5">
         <v>1728</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="5">
         <v>1377</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="5">
         <v>925</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="5">
         <v>213</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="5">
         <v>4099</v>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
+      <c r="G65" s="5">
+        <v>0</v>
+      </c>
+      <c r="H65" s="5">
         <v>28</v>
       </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
+      <c r="I65" s="5">
+        <v>0</v>
+      </c>
+      <c r="J65" s="6">
         <v>6.7</v>
       </c>
-      <c r="K65">
+      <c r="K65" s="5">
         <v>4285</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
-      <c r="A66" s="2">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+      <c r="A66" s="4">
         <v>45742</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="5">
         <v>1789</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="5">
         <v>1402</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="5">
         <v>997</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="5">
         <v>217</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="5">
         <v>4285</v>
       </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
+      <c r="G66" s="5">
+        <v>0</v>
+      </c>
+      <c r="H66" s="6">
         <v>29.5</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
+      <c r="I66" s="5">
+        <v>0</v>
+      </c>
+      <c r="J66" s="6">
         <v>5.6</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="5">
         <v>4361</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
-      <c r="A67" s="2">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+      <c r="A67" s="4">
         <v>45743</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="5">
         <v>1814</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="5">
         <v>1472</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="5">
         <v>1050</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="5">
         <v>224</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="5">
         <v>4361</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
+      <c r="G67" s="5">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6">
         <v>29.3</v>
       </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
+      <c r="I67" s="5">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6">
         <v>7.8</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="5">
         <v>4302</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
-      <c r="A68" s="2">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+      <c r="A68" s="4">
         <v>45744</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="5">
         <v>1760</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="5">
         <v>1416</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="5">
         <v>968</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="5">
         <v>201</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="5">
         <v>4302</v>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
+      <c r="G68" s="5">
+        <v>0</v>
+      </c>
+      <c r="H68" s="6">
         <v>25.2</v>
       </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
+      <c r="I68" s="5">
+        <v>0</v>
+      </c>
+      <c r="J68" s="6">
         <v>14.7</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="5">
         <v>3640</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
-      <c r="A69" s="2">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+      <c r="A69" s="4">
         <v>45745</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="5">
         <v>1559</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="5">
         <v>1146</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="5">
         <v>855</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="5">
         <v>157</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="5">
         <v>3640</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
+      <c r="G69" s="5">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6">
         <v>22.3</v>
       </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
+      <c r="I69" s="5">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6">
         <v>15.3</v>
       </c>
-      <c r="K69">
+      <c r="K69" s="5">
         <v>3777</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
-      <c r="A70" s="2">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+      <c r="A70" s="4">
         <v>45746</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="5">
         <v>1492</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="5">
         <v>1253</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="5">
         <v>872</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="5">
         <v>141</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="5">
         <v>3777</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
+      <c r="G70" s="5">
+        <v>0</v>
+      </c>
+      <c r="H70" s="6">
         <v>24.2</v>
       </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
+      <c r="I70" s="5">
+        <v>0</v>
+      </c>
+      <c r="J70" s="6">
         <v>12.9</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="5">
         <v>3707</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
-      <c r="A71" s="2">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+      <c r="A71" s="4">
         <v>45747</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="5">
         <v>1581</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="5">
         <v>1223</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="5">
         <v>820</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="5">
         <v>148</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="5">
         <v>3707</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="5">
         <v>1</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="6">
         <v>25.8</v>
       </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
+      <c r="I71" s="5">
+        <v>0</v>
+      </c>
+      <c r="J71" s="5">
         <v>10</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="5">
         <v>3919</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
-      <c r="A72" s="2">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+      <c r="A72" s="4">
         <v>45748</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="5">
         <v>1660</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="5">
         <v>1291</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="5">
         <v>822</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="5">
         <v>190</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="5">
         <v>3919</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="5">
         <v>1</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="6">
         <v>26.6</v>
       </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
+      <c r="I72" s="5">
+        <v>0</v>
+      </c>
+      <c r="J72" s="6">
         <v>10.4</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="5">
         <v>4052</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="2">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+      <c r="A73" s="4">
         <v>45749</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="5">
         <v>1730</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="5">
         <v>1309</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="5">
         <v>914</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="5">
         <v>202</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="5">
         <v>4052</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
+      <c r="G73" s="5">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5">
         <v>27</v>
       </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
+      <c r="I73" s="5">
+        <v>0</v>
+      </c>
+      <c r="J73" s="5">
         <v>6</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="5">
         <v>4186</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
-      <c r="A74" s="2">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+      <c r="A74" s="4">
         <v>45750</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="5">
         <v>1749</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="5">
         <v>1365</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="5">
         <v>944</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="5">
         <v>235</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="5">
         <v>4186</v>
       </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
+      <c r="G74" s="5">
+        <v>0</v>
+      </c>
+      <c r="H74" s="6">
         <v>29.3</v>
       </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
+      <c r="I74" s="5">
+        <v>0</v>
+      </c>
+      <c r="J74" s="6">
         <v>6.9</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="5">
         <v>4306</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
-      <c r="A75" s="2">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+      <c r="A75" s="4">
         <v>45751</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="5">
         <v>1785</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="5">
         <v>1373</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="5">
         <v>963</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="5">
         <v>248</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="5">
         <v>4306</v>
       </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="H75">
+      <c r="G75" s="5">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6">
         <v>30.1</v>
       </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K75">
+      <c r="I75" s="5">
+        <v>0</v>
+      </c>
+      <c r="J75" s="6">
+        <v>8.3</v>
+      </c>
+      <c r="K75" s="5">
         <v>4049</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
-      <c r="A76" s="2">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+      <c r="A76" s="4">
         <v>45752</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="5">
         <v>1765</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="5">
         <v>1193</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="5">
         <v>951</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="5">
         <v>196</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="5">
         <v>4049</v>
       </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="H76">
+      <c r="G76" s="5">
+        <v>0</v>
+      </c>
+      <c r="H76" s="6">
         <v>28.6</v>
       </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
+      <c r="I76" s="5">
+        <v>0</v>
+      </c>
+      <c r="J76" s="6">
         <v>10.7</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="5">
         <v>3954</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
-      <c r="A77" s="2">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+      <c r="A77" s="4">
         <v>45753</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="5">
         <v>1671</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="5">
         <v>1228</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="5">
         <v>897</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="5">
         <v>170</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="5">
         <v>3954</v>
       </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="H77">
+      <c r="G77" s="5">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6">
         <v>29.5</v>
       </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77">
+      <c r="I77" s="5">
+        <v>0</v>
+      </c>
+      <c r="J77" s="6">
         <v>4.6</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="5">
         <v>4756</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
-      <c r="A78" s="2">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+      <c r="A78" s="4">
         <v>45754</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="5">
         <v>1923</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="5">
         <v>1583</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="5">
         <v>982</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="5">
         <v>284</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="5">
         <v>4756</v>
       </c>
-      <c r="G78">
-        <v>0</v>
-      </c>
-      <c r="H78">
+      <c r="G78" s="5">
+        <v>0</v>
+      </c>
+      <c r="H78" s="6">
         <v>31.7</v>
       </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="J78">
+      <c r="I78" s="5">
+        <v>0</v>
+      </c>
+      <c r="J78" s="6">
         <v>5.9</v>
       </c>
-      <c r="K78">
+      <c r="K78" s="5">
         <v>5029</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
-      <c r="A79" s="2">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+      <c r="A79" s="4">
         <v>45755</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="5">
         <v>2133</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="5">
         <v>1679</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="5">
         <v>1116</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="5">
         <v>292</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="5">
         <v>5029</v>
       </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
-      <c r="H79">
+      <c r="G79" s="5">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6">
         <v>32.7</v>
       </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
+      <c r="I79" s="5">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6">
         <v>10.8</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="5">
         <v>5462</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="2">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+      <c r="A80" s="4">
         <v>45756</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="5">
         <v>2373</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="5">
         <v>1849</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="5">
         <v>1373</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="5">
         <v>285</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="5">
         <v>5462</v>
       </c>
-      <c r="G80">
-        <v>0</v>
-      </c>
-      <c r="H80">
+      <c r="G80" s="5">
+        <v>0</v>
+      </c>
+      <c r="H80" s="6">
         <v>33.7</v>
       </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-      <c r="J80">
+      <c r="I80" s="5">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5">
         <v>9</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="5">
         <v>5278</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
-      <c r="A81" s="2">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+      <c r="A81" s="4">
         <v>45757</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="5">
         <v>2273</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="5">
         <v>1740</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="5">
         <v>1242</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="5">
         <v>198</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="5">
         <v>5278</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="5">
         <v>1</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="6">
         <v>32.4</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="6">
         <v>1.9</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="6">
         <v>8.5</v>
       </c>
-      <c r="K81">
+      <c r="K81" s="5">
         <v>5102</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="2">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+      <c r="A82" s="4">
         <v>45758</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="5">
         <v>2144</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="5">
         <v>1657</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="5">
         <v>1144</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="5">
         <v>253</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="5">
         <v>5102</v>
       </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82">
+      <c r="G82" s="5">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5">
         <v>27</v>
       </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
+      <c r="I82" s="5">
+        <v>0</v>
+      </c>
+      <c r="J82" s="6">
         <v>17.8</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="5">
         <v>4300</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="2">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+      <c r="A83" s="4">
         <v>45759</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="5">
         <v>1929</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="5">
         <v>1305</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="5">
         <v>1029</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="5">
         <v>189</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="5">
         <v>4300</v>
       </c>
-      <c r="G83">
-        <v>0</v>
-      </c>
-      <c r="H83">
+      <c r="G83" s="5">
+        <v>0</v>
+      </c>
+      <c r="H83" s="6">
         <v>27.6</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="5">
         <v>2</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="6">
         <v>9.5</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="5">
         <v>4173</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="2">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+      <c r="A84" s="4">
         <v>45760</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="5">
         <v>1883</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="5">
         <v>1354</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="5">
         <v>988</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="5">
         <v>167</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="5">
         <v>4173</v>
       </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
-      <c r="H84">
+      <c r="G84" s="5">
+        <v>0</v>
+      </c>
+      <c r="H84" s="6">
         <v>29.3</v>
       </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
+      <c r="I84" s="5">
+        <v>0</v>
+      </c>
+      <c r="J84" s="6">
         <v>5.9</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="5">
         <v>4671</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="2">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+      <c r="A85" s="4">
         <v>45761</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="5">
         <v>2036</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="5">
         <v>1546</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="5">
         <v>1052</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="5">
         <v>192</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="5">
         <v>4671</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="5">
         <v>1</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="6">
         <v>30.1</v>
       </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
+      <c r="I85" s="5">
+        <v>0</v>
+      </c>
+      <c r="J85" s="6">
         <v>9.1</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="5">
         <v>5157</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="2">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+      <c r="A86" s="4">
         <v>45762</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="5">
         <v>2236</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="5">
         <v>1656</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="5">
         <v>1160</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="5">
         <v>248</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="5">
         <v>5157</v>
       </c>
-      <c r="G86">
-        <v>0</v>
-      </c>
-      <c r="H86">
+      <c r="G86" s="5">
+        <v>0</v>
+      </c>
+      <c r="H86" s="6">
         <v>30.9</v>
       </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
+      <c r="I86" s="5">
+        <v>0</v>
+      </c>
+      <c r="J86" s="5">
         <v>9</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="5">
         <v>5436</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="2">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+      <c r="A87" s="4">
         <v>45763</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="5">
         <v>2358</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="5">
         <v>1710</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="5">
         <v>1251</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="5">
         <v>260</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="5">
         <v>5436</v>
       </c>
-      <c r="G87">
-        <v>0</v>
-      </c>
-      <c r="H87">
+      <c r="G87" s="5">
+        <v>0</v>
+      </c>
+      <c r="H87" s="6">
         <v>32.1</v>
       </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="J87">
+      <c r="I87" s="5">
+        <v>0</v>
+      </c>
+      <c r="J87" s="6">
         <v>9.6</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="5">
         <v>5699</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="2">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+      <c r="A88" s="4">
         <v>45764</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="5">
         <v>2498</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="5">
         <v>1805</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="5">
         <v>1297</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="5">
         <v>292</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="5">
         <v>5699</v>
       </c>
-      <c r="G88">
-        <v>0</v>
-      </c>
-      <c r="H88">
+      <c r="G88" s="5">
+        <v>0</v>
+      </c>
+      <c r="H88" s="6">
         <v>33.3</v>
       </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K88">
+      <c r="I88" s="5">
+        <v>0</v>
+      </c>
+      <c r="J88" s="6">
+        <v>8.8</v>
+      </c>
+      <c r="K88" s="5">
         <v>5613</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="2">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+      <c r="A89" s="4">
         <v>45765</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="5">
         <v>2449</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="5">
         <v>1808</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="5">
         <v>1279</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="5">
         <v>204</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="5">
         <v>5613</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="5">
         <v>1</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="6">
         <v>32.3</v>
       </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
+      <c r="I89" s="5">
+        <v>0</v>
+      </c>
+      <c r="J89" s="6">
         <v>11.8</v>
       </c>
-      <c r="K89">
+      <c r="K89" s="5">
         <v>5489</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="2">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+      <c r="A90" s="4">
         <v>45766</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="5">
         <v>2454</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="5">
         <v>1621</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="5">
         <v>1312</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="5">
         <v>265</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="5">
         <v>5489</v>
       </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
-      <c r="H90">
+      <c r="G90" s="5">
+        <v>0</v>
+      </c>
+      <c r="H90" s="6">
         <v>31.8</v>
       </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
+      <c r="I90" s="5">
+        <v>0</v>
+      </c>
+      <c r="J90" s="6">
         <v>16.8</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="5">
         <v>5635</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="2">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+      <c r="A91" s="4">
         <v>45767</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="5">
         <v>2580</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="5">
         <v>1689</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="5">
         <v>1309</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="5">
         <v>210</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="5">
         <v>5635</v>
       </c>
-      <c r="G91">
-        <v>0</v>
-      </c>
-      <c r="H91">
+      <c r="G91" s="5">
+        <v>0</v>
+      </c>
+      <c r="H91" s="6">
         <v>32.6</v>
       </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
+      <c r="I91" s="5">
+        <v>0</v>
+      </c>
+      <c r="J91" s="6">
         <v>12.3</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="5">
         <v>5764</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="2">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+      <c r="A92" s="4">
         <v>45768</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="5">
         <v>2507</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="5">
         <v>1778</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="5">
         <v>1263</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="5">
         <v>330</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="5">
         <v>5764</v>
       </c>
-      <c r="G92">
-        <v>0</v>
-      </c>
-      <c r="H92">
+      <c r="G92" s="5">
+        <v>0</v>
+      </c>
+      <c r="H92" s="6">
         <v>33.2</v>
       </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
-      <c r="J92">
+      <c r="I92" s="5">
+        <v>0</v>
+      </c>
+      <c r="J92" s="6">
         <v>8.9</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="5">
         <v>5581</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="2">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+      <c r="A93" s="4">
         <v>45769</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="5">
         <v>2414</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="5">
         <v>1729</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="5">
         <v>1224</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="5">
         <v>308</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="5">
         <v>5581</v>
       </c>
-      <c r="G93">
-        <v>0</v>
-      </c>
-      <c r="H93">
+      <c r="G93" s="5">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6">
         <v>31.8</v>
       </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
+      <c r="I93" s="5">
+        <v>0</v>
+      </c>
+      <c r="J93" s="6">
         <v>10.2</v>
       </c>
-      <c r="K93">
+      <c r="K93" s="5">
         <v>5645</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="2">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="4">
         <v>45770</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="5">
         <v>2415</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="5">
         <v>1698</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="5">
         <v>1226</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="5">
         <v>284</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="5">
         <v>5645</v>
       </c>
-      <c r="G94">
-        <v>0</v>
-      </c>
-      <c r="H94">
+      <c r="G94" s="5">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6">
         <v>31.6</v>
       </c>
-      <c r="I94">
-        <v>0</v>
-      </c>
-      <c r="J94">
+      <c r="I94" s="5">
+        <v>0</v>
+      </c>
+      <c r="J94" s="6">
         <v>10.3</v>
       </c>
-      <c r="K94">
+      <c r="K94" s="5">
         <v>5737</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="2">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+      <c r="A95" s="4">
         <v>45771</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="5">
         <v>2534</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="5">
         <v>1744</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="5">
         <v>1252</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="5">
         <v>285</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="5">
         <v>5737</v>
       </c>
-      <c r="G95">
-        <v>0</v>
-      </c>
-      <c r="H95">
+      <c r="G95" s="5">
+        <v>0</v>
+      </c>
+      <c r="H95" s="6">
         <v>32.6</v>
       </c>
-      <c r="I95">
-        <v>0</v>
-      </c>
-      <c r="J95">
+      <c r="I95" s="5">
+        <v>0</v>
+      </c>
+      <c r="J95" s="6">
         <v>8.1</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="5">
         <v>5780</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="2">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+      <c r="A96" s="4">
         <v>45772</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="5">
         <v>2543</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="5">
         <v>1772</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="5">
         <v>1227</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="5">
         <v>302</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="5">
         <v>5780</v>
       </c>
-      <c r="G96">
-        <v>0</v>
-      </c>
-      <c r="H96">
+      <c r="G96" s="5">
+        <v>0</v>
+      </c>
+      <c r="H96" s="6">
         <v>33.2</v>
       </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-      <c r="J96">
+      <c r="I96" s="5">
+        <v>0</v>
+      </c>
+      <c r="J96" s="6">
         <v>7.9</v>
       </c>
-      <c r="K96">
+      <c r="K96" s="5">
         <v>5550</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
-      <c r="A97" s="2">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+      <c r="A97" s="4">
         <v>45773</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="5">
         <v>2518</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="5">
         <v>1609</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="5">
         <v>1290</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="5">
         <v>220</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="5">
         <v>5550</v>
       </c>
-      <c r="G97">
-        <v>0</v>
-      </c>
-      <c r="H97">
+      <c r="G97" s="5">
+        <v>0</v>
+      </c>
+      <c r="H97" s="6">
         <v>32.8</v>
       </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97">
+      <c r="I97" s="5">
+        <v>0</v>
+      </c>
+      <c r="J97" s="6">
         <v>7.7</v>
       </c>
-      <c r="K97">
+      <c r="K97" s="5">
         <v>5710</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
-      <c r="A98" s="2">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+      <c r="A98" s="4">
         <v>45774</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="5">
         <v>2577</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="5">
         <v>1640</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="5">
         <v>1269</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="5">
         <v>175</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="5">
         <v>5710</v>
       </c>
-      <c r="G98">
-        <v>0</v>
-      </c>
-      <c r="H98">
+      <c r="G98" s="5">
+        <v>0</v>
+      </c>
+      <c r="H98" s="6">
         <v>33.4</v>
       </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
+      <c r="I98" s="5">
+        <v>0</v>
+      </c>
+      <c r="J98" s="6">
         <v>6.6</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="5">
         <v>6015</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
-      <c r="A99" s="2">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+      <c r="A99" s="4">
         <v>45775</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="5">
         <v>2694</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="5">
         <v>1811</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="5">
         <v>1296</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="5">
         <v>294</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="5">
         <v>6015</v>
       </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-      <c r="H99">
+      <c r="G99" s="5">
+        <v>0</v>
+      </c>
+      <c r="H99" s="6">
         <v>33.2</v>
       </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99">
+      <c r="I99" s="5">
+        <v>0</v>
+      </c>
+      <c r="J99" s="6">
         <v>11.5</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="5">
         <v>5760</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
-      <c r="A100" s="2">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+      <c r="A100" s="4">
         <v>45776</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="5">
         <v>2633</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="5">
         <v>1717</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="5">
         <v>1274</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="5">
         <v>328</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="5">
         <v>5760</v>
       </c>
-      <c r="G100">
-        <v>0</v>
-      </c>
-      <c r="H100">
+      <c r="G100" s="5">
+        <v>0</v>
+      </c>
+      <c r="H100" s="6">
         <v>30.6</v>
       </c>
-      <c r="I100">
-        <v>0</v>
-      </c>
-      <c r="J100">
+      <c r="I100" s="5">
+        <v>0</v>
+      </c>
+      <c r="J100" s="6">
         <v>15.1</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="5">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
-      <c r="A101" s="2">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+      <c r="A101" s="4">
         <v>45777</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="5">
         <v>2668</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="5">
         <v>1841</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="5">
         <v>1410</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="5">
         <v>338</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="5">
         <v>6000</v>
       </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
+      <c r="G101" s="5">
+        <v>0</v>
+      </c>
+      <c r="H101" s="6">
         <v>31.3</v>
       </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
+      <c r="I101" s="5">
+        <v>0</v>
+      </c>
+      <c r="J101" s="6">
         <v>14.3</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="5">
         <v>6108</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
-      <c r="A102" s="2">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+      <c r="A102" s="4">
         <v>45778</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="5">
         <v>2747</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="5">
         <v>1841</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="5">
         <v>1317</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="5">
         <v>325</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="5">
         <v>6108</v>
       </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-      <c r="H102">
+      <c r="G102" s="5">
+        <v>0</v>
+      </c>
+      <c r="H102" s="6">
         <v>32.2</v>
       </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
-      <c r="J102">
+      <c r="I102" s="5">
+        <v>0</v>
+      </c>
+      <c r="J102" s="6">
         <v>14.4</v>
       </c>
-      <c r="K102">
+      <c r="K102" s="5">
         <v>5871</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
-      <c r="A103" s="2">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+      <c r="A103" s="4">
         <v>45779</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="5">
         <v>2680</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="5">
         <v>1669</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="5">
         <v>1268</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="5">
         <v>272</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="5">
         <v>5871</v>
       </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-      <c r="H103">
+      <c r="G103" s="5">
+        <v>0</v>
+      </c>
+      <c r="H103" s="6">
         <v>24.1</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="5">
         <v>46</v>
       </c>
-      <c r="J103">
+      <c r="J103" s="6">
         <v>12.8</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="5">
         <v>4709</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
-      <c r="A104" s="2">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+      <c r="A104" s="4">
         <v>45780</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="5">
         <v>2166</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="5">
         <v>1340</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="5">
         <v>1095</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="5">
         <v>234</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="5">
         <v>4709</v>
       </c>
-      <c r="G104">
-        <v>0</v>
-      </c>
-      <c r="H104">
+      <c r="G104" s="5">
+        <v>0</v>
+      </c>
+      <c r="H104" s="6">
         <v>28.8</v>
       </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K104">
+      <c r="I104" s="5">
+        <v>0</v>
+      </c>
+      <c r="J104" s="6">
+        <v>9.2</v>
+      </c>
+      <c r="K104" s="5">
         <v>4829</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
-      <c r="A105" s="2">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+      <c r="A105" s="4">
         <v>45781</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="5">
         <v>2201</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="5">
         <v>1411</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="5">
         <v>1070</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="5">
         <v>291</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="5">
         <v>4829</v>
       </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-      <c r="H105">
+      <c r="G105" s="5">
+        <v>0</v>
+      </c>
+      <c r="H105" s="6">
         <v>30.3</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="5">
         <v>1</v>
       </c>
-      <c r="J105">
+      <c r="J105" s="6">
         <v>8.5</v>
       </c>
-      <c r="K105">
+      <c r="K105" s="5">
         <v>4879</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
-      <c r="A106" s="2">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+      <c r="A106" s="4">
         <v>45782</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="5">
         <v>2115</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="5">
         <v>1515</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="5">
         <v>1025</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="5">
         <v>288</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="5">
         <v>4879</v>
       </c>
-      <c r="G106">
-        <v>0</v>
-      </c>
-      <c r="H106">
+      <c r="G106" s="5">
+        <v>0</v>
+      </c>
+      <c r="H106" s="6">
         <v>27.4</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="6">
         <v>0.5</v>
       </c>
-      <c r="J106">
+      <c r="J106" s="6">
         <v>13.4</v>
       </c>
-      <c r="K106">
+      <c r="K106" s="5">
         <v>5113</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
-      <c r="A107" s="2">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+      <c r="A107" s="4">
         <v>45783</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="5">
         <v>2198</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="5">
         <v>1618</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="5">
         <v>1122</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="5">
         <v>293</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="5">
         <v>5113</v>
       </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-      <c r="H107">
+      <c r="G107" s="5">
+        <v>0</v>
+      </c>
+      <c r="H107" s="6">
         <v>28.9</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="6">
         <v>0.2</v>
       </c>
-      <c r="J107">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K107">
+      <c r="J107" s="6">
+        <v>9.2</v>
+      </c>
+      <c r="K107" s="5">
         <v>5425</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
-      <c r="A108" s="2">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+      <c r="A108" s="4">
         <v>45784</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="5">
         <v>2259</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="5">
         <v>1666</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="5">
         <v>1207</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="5">
         <v>288</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="5">
         <v>5425</v>
       </c>
-      <c r="G108">
-        <v>0</v>
-      </c>
-      <c r="H108">
+      <c r="G108" s="5">
+        <v>0</v>
+      </c>
+      <c r="H108" s="6">
         <v>29.2</v>
       </c>
-      <c r="I108">
+      <c r="I108" s="6">
         <v>0.8</v>
       </c>
-      <c r="J108">
+      <c r="J108" s="6">
         <v>11.2</v>
       </c>
-      <c r="K108">
+      <c r="K108" s="5">
         <v>5507</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
-      <c r="A109" s="2">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+      <c r="A109" s="4">
         <v>45785</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="5">
         <v>2438</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="5">
         <v>1671</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="5">
         <v>1214</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="5">
         <v>290</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="5">
         <v>5507</v>
       </c>
-      <c r="G109">
-        <v>0</v>
-      </c>
-      <c r="H109">
+      <c r="G109" s="5">
+        <v>0</v>
+      </c>
+      <c r="H109" s="6">
         <v>30.7</v>
       </c>
-      <c r="I109">
+      <c r="I109" s="6">
         <v>0.5</v>
       </c>
-      <c r="J109">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K109">
+      <c r="J109" s="6">
+        <v>9.8</v>
+      </c>
+      <c r="K109" s="5">
         <v>5765</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
-      <c r="A110" s="2">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+      <c r="A110" s="4">
         <v>45786</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="5">
         <v>2556</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="5">
         <v>1756</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="5">
         <v>1286</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="5">
         <v>285</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="5">
         <v>5765</v>
       </c>
-      <c r="G110">
-        <v>0</v>
-      </c>
-      <c r="H110">
+      <c r="G110" s="5">
+        <v>0</v>
+      </c>
+      <c r="H110" s="6">
         <v>31.2</v>
       </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
-      <c r="J110">
+      <c r="I110" s="5">
+        <v>0</v>
+      </c>
+      <c r="J110" s="6">
         <v>8.5</v>
       </c>
-      <c r="K110">
+      <c r="K110" s="5">
         <v>5551</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
-      <c r="A111" s="2">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+      <c r="A111" s="4">
         <v>45787</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="5">
         <v>2485</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="5">
         <v>1599</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="5">
         <v>1275</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="5">
         <v>239</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="5">
         <v>5551</v>
       </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-      <c r="H111">
+      <c r="G111" s="5">
+        <v>0</v>
+      </c>
+      <c r="H111" s="6">
         <v>29.6</v>
       </c>
-      <c r="I111">
+      <c r="I111" s="6">
         <v>5.1</v>
       </c>
-      <c r="J111">
+      <c r="J111" s="6">
         <v>6.9</v>
       </c>
-      <c r="K111">
+      <c r="K111" s="5">
         <v>5224</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
-      <c r="A112" s="2">
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+      <c r="A112" s="4">
         <v>45788</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="5">
         <v>2416</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="5">
         <v>1523</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="5">
         <v>1162</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="5">
         <v>211</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="5">
         <v>5224</v>
       </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-      <c r="H112">
+      <c r="G112" s="5">
+        <v>0</v>
+      </c>
+      <c r="H112" s="6">
         <v>31.7</v>
       </c>
-      <c r="I112">
+      <c r="I112" s="5">
         <v>3</v>
       </c>
-      <c r="J112">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K112">
+      <c r="J112" s="6">
+        <v>8.7</v>
+      </c>
+      <c r="K112" s="5">
         <v>5839</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
-      <c r="A113" s="2">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+      <c r="A113" s="4">
         <v>45789</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="5">
         <v>2646</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="5">
         <v>1788</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="5">
         <v>1288</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="5">
         <v>225</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="5">
         <v>5839</v>
       </c>
-      <c r="G113">
+      <c r="G113" s="5">
         <v>1</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="6">
         <v>32.8</v>
       </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
+      <c r="I113" s="5">
+        <v>0</v>
+      </c>
+      <c r="J113" s="6">
         <v>10.4</v>
       </c>
-      <c r="K113">
+      <c r="K113" s="5">
         <v>6401</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
-      <c r="A114" s="2">
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+      <c r="A114" s="4">
         <v>45790</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="5">
         <v>2796</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="5">
         <v>1895</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="5">
         <v>1376</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="5">
         <v>293</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="5">
         <v>6401</v>
       </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-      <c r="H114">
+      <c r="G114" s="5">
+        <v>0</v>
+      </c>
+      <c r="H114" s="6">
         <v>31.7</v>
       </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
+      <c r="I114" s="5">
+        <v>0</v>
+      </c>
+      <c r="J114" s="6">
         <v>11.5</v>
       </c>
-      <c r="K114">
+      <c r="K114" s="5">
         <v>6168</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
-      <c r="A115" s="2">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+      <c r="A115" s="4">
         <v>45791</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="5">
         <v>2742</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="5">
         <v>1822</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="5">
         <v>1363</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="5">
         <v>303</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="5">
         <v>6168</v>
       </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115">
+      <c r="G115" s="5">
+        <v>0</v>
+      </c>
+      <c r="H115" s="6">
         <v>32.8</v>
       </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="K115">
+      <c r="I115" s="5">
+        <v>0</v>
+      </c>
+      <c r="J115" s="6">
+        <v>9.3</v>
+      </c>
+      <c r="K115" s="5">
         <v>6474</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
-      <c r="A116" s="2">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+      <c r="A116" s="4">
         <v>45792</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="5">
         <v>2955</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="5">
         <v>1953</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="5">
         <v>1447</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="5">
         <v>304</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="5">
         <v>6474</v>
       </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-      <c r="H116">
+      <c r="G116" s="5">
+        <v>0</v>
+      </c>
+      <c r="H116" s="6">
         <v>34.3</v>
       </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
+      <c r="I116" s="5">
+        <v>0</v>
+      </c>
+      <c r="J116" s="5">
         <v>9</v>
       </c>
-      <c r="K116">
+      <c r="K116" s="5">
         <v>6867</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
-      <c r="A117" s="2">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+      <c r="A117" s="4">
         <v>45793</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="5">
         <v>3004</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="5">
         <v>2009</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="5">
         <v>1479</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="5">
         <v>356</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="5">
         <v>6867</v>
       </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
+      <c r="G117" s="5">
+        <v>0</v>
+      </c>
+      <c r="H117" s="6">
         <v>34.2</v>
       </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K117">
+      <c r="I117" s="5">
+        <v>0</v>
+      </c>
+      <c r="J117" s="6">
+        <v>9.8</v>
+      </c>
+      <c r="K117" s="5">
         <v>6238</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
-      <c r="A118" s="2">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
+      <c r="A118" s="4">
         <v>45794</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="5">
         <v>2760</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="5">
         <v>1791</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="5">
         <v>1457</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="5">
         <v>282</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="5">
         <v>6238</v>
       </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
+      <c r="G118" s="5">
+        <v>0</v>
+      </c>
+      <c r="H118" s="6">
         <v>33.8</v>
       </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
+      <c r="I118" s="5">
+        <v>0</v>
+      </c>
+      <c r="J118" s="6">
         <v>10.6</v>
       </c>
-      <c r="K118">
+      <c r="K118" s="5">
         <v>6851</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
-      <c r="A119" s="2">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+      <c r="A119" s="4">
         <v>45795</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="5">
         <v>3176</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="5">
         <v>1924</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="5">
         <v>1486</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="5">
         <v>220</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="5">
         <v>6851</v>
       </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
+      <c r="G119" s="5">
+        <v>0</v>
+      </c>
+      <c r="H119" s="6">
         <v>35.4</v>
       </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
+      <c r="I119" s="5">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5">
         <v>10</v>
       </c>
-      <c r="K119">
+      <c r="K119" s="5">
         <v>7265</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
-      <c r="A120" s="2">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+      <c r="A120" s="4">
         <v>45796</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="5">
         <v>3369</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="5">
         <v>2136</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="5">
         <v>1596</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="5">
         <v>390</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="5">
         <v>7265</v>
       </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
+      <c r="G120" s="5">
+        <v>0</v>
+      </c>
+      <c r="H120" s="6">
         <v>34.1</v>
       </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
+      <c r="I120" s="5">
+        <v>0</v>
+      </c>
+      <c r="J120" s="5">
         <v>12</v>
       </c>
-      <c r="K120">
+      <c r="K120" s="5">
         <v>7533</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
-      <c r="A121" s="2">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+      <c r="A121" s="4">
         <v>45797</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="5">
         <v>3488</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="5">
         <v>2211</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="5">
         <v>1645</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="5">
         <v>405</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="5">
         <v>7533</v>
       </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
+      <c r="G121" s="5">
+        <v>0</v>
+      </c>
+      <c r="H121" s="5">
         <v>35</v>
       </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
+      <c r="I121" s="5">
+        <v>0</v>
+      </c>
+      <c r="J121" s="6">
         <v>11.2</v>
       </c>
-      <c r="K121">
+      <c r="K121" s="5">
         <v>7748</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
-      <c r="A122" s="2">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
+      <c r="A122" s="4">
         <v>45798</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="5">
         <v>3427</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="5">
         <v>2317</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="5">
         <v>1667</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="5">
         <v>387</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="5">
         <v>7748</v>
       </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
+      <c r="G122" s="5">
+        <v>0</v>
+      </c>
+      <c r="H122" s="6">
         <v>33.8</v>
       </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
+      <c r="I122" s="5">
+        <v>0</v>
+      </c>
+      <c r="J122" s="6">
         <v>12.5</v>
       </c>
-      <c r="K122">
+      <c r="K122" s="5">
         <v>6297</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
-      <c r="A123" s="2">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+      <c r="A123" s="4">
         <v>45800</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="5">
         <v>2965</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="5">
         <v>1951</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="5">
         <v>1465</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="5">
         <v>360</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="5">
         <v>6658</v>
       </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
+      <c r="G123" s="5">
+        <v>0</v>
+      </c>
+      <c r="H123" s="6">
         <v>31.6</v>
       </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
+      <c r="I123" s="5">
+        <v>0</v>
+      </c>
+      <c r="J123" s="6">
         <v>15.1</v>
       </c>
-      <c r="K123">
+      <c r="K123" s="5">
         <v>6851</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
-      <c r="A124" s="2">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+      <c r="A124" s="4">
         <v>45801</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="5">
         <v>3199</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="5">
         <v>2130</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="5">
         <v>1669</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="5">
         <v>292</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="5">
         <v>6851</v>
       </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
+      <c r="G124" s="5">
+        <v>0</v>
+      </c>
+      <c r="H124" s="6">
         <v>33.7</v>
       </c>
-      <c r="I124">
+      <c r="I124" s="6">
         <v>0.1</v>
       </c>
-      <c r="J124">
+      <c r="J124" s="6">
         <v>16.9</v>
       </c>
-      <c r="K124">
+      <c r="K124" s="5">
         <v>6796</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
-      <c r="A125" s="2">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
+      <c r="A125" s="4">
         <v>45802</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="5">
         <v>3177</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="5">
         <v>1986</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="5">
         <v>1597</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="5">
         <v>210</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="5">
         <v>6796</v>
       </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
+      <c r="G125" s="5">
+        <v>0</v>
+      </c>
+      <c r="H125" s="6">
         <v>27.4</v>
       </c>
-      <c r="I125">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="J125">
+      <c r="I125" s="6">
+        <v>69.1</v>
+      </c>
+      <c r="J125" s="6">
         <v>12.6</v>
       </c>
-      <c r="K125">
+      <c r="K125" s="5">
         <v>6108</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
-      <c r="A126" s="2">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
+      <c r="A126" s="4">
         <v>45803</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="5">
         <v>2793</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="5">
         <v>1815</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="5">
         <v>1363</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="5">
         <v>327</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="5">
         <v>6108</v>
       </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
+      <c r="G126" s="5">
+        <v>0</v>
+      </c>
+      <c r="H126" s="5">
         <v>30</v>
       </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
+      <c r="I126" s="5">
+        <v>0</v>
+      </c>
+      <c r="J126" s="6">
         <v>9.5</v>
       </c>
-      <c r="K126">
+      <c r="K126" s="5">
         <v>6690</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
-      <c r="A127" s="2">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+      <c r="A127" s="4">
         <v>45804</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="5">
         <v>3143</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="5">
         <v>2306</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="5">
         <v>1419</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="5">
         <v>330</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="5">
         <v>6690</v>
       </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
+      <c r="G127" s="5">
+        <v>0</v>
+      </c>
+      <c r="H127" s="6">
         <v>32.1</v>
       </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
+      <c r="I127" s="5">
+        <v>0</v>
+      </c>
+      <c r="J127" s="6">
         <v>7.2</v>
       </c>
-      <c r="K127">
+      <c r="K127" s="5">
         <v>7015</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
-      <c r="A128" s="2">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
+      <c r="A128" s="4">
         <v>45805</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="5">
         <v>3274</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="5">
         <v>2159</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="5">
         <v>1539</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="5">
         <v>340</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="5">
         <v>7015</v>
       </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
+      <c r="G128" s="5">
+        <v>0</v>
+      </c>
+      <c r="H128" s="6">
         <v>33.6</v>
       </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
+      <c r="I128" s="5">
+        <v>0</v>
+      </c>
+      <c r="J128" s="6">
         <v>6.2</v>
       </c>
-      <c r="K128">
+      <c r="K128" s="5">
         <v>7360</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
-      <c r="A129" s="2">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+      <c r="A129" s="4">
         <v>45806</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="5">
         <v>3226</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="5">
         <v>2221</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="5">
         <v>1612</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="5">
         <v>338</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="5">
         <v>7360</v>
       </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
+      <c r="G129" s="5">
+        <v>0</v>
+      </c>
+      <c r="H129" s="6">
         <v>32.7</v>
       </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
+      <c r="I129" s="5">
+        <v>0</v>
+      </c>
+      <c r="J129" s="6">
         <v>8.4</v>
       </c>
-      <c r="K129">
+      <c r="K129" s="5">
         <v>6304</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
-      <c r="A130" s="2">
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
+      <c r="A130" s="4">
         <v>45807</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="5">
         <v>2892</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="5">
         <v>1791</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="5">
         <v>1360</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="5">
         <v>315</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="5">
         <v>6304</v>
       </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
+      <c r="G130" s="5">
+        <v>0</v>
+      </c>
+      <c r="H130" s="6">
         <v>31.1</v>
       </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K130">
+      <c r="I130" s="5">
+        <v>0</v>
+      </c>
+      <c r="J130" s="6">
+        <v>8.7</v>
+      </c>
+      <c r="K130" s="5">
         <v>6391</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
-      <c r="A131" s="2">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
+      <c r="A131" s="4">
         <v>45808</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="5">
         <v>2848</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="5">
         <v>1824</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="5">
         <v>1431</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="5">
         <v>263</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="5">
         <v>6391</v>
       </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
+      <c r="G131" s="5">
+        <v>0</v>
+      </c>
+      <c r="H131" s="6">
         <v>32.2</v>
       </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
+      <c r="I131" s="5">
+        <v>0</v>
+      </c>
+      <c r="J131" s="6">
         <v>5.6</v>
       </c>
-      <c r="K131">
+      <c r="K131" s="5">
         <v>5726</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
-      <c r="A132" s="2">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
+      <c r="A132" s="4">
         <v>45810</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="5">
         <v>2547</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="5">
         <v>1887</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="5">
         <v>1290</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="5">
         <v>317</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="5">
         <v>5893</v>
       </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
+      <c r="G132" s="5">
+        <v>0</v>
+      </c>
+      <c r="H132" s="6">
         <v>30.1</v>
       </c>
-      <c r="I132">
+      <c r="I132" s="6">
         <v>0.2</v>
       </c>
-      <c r="J132">
+      <c r="J132" s="6">
         <v>7.1</v>
       </c>
-      <c r="K132">
+      <c r="K132" s="5">
         <v>5548</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
-      <c r="A133" s="2">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
+      <c r="A133" s="4">
         <v>45811</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="5">
         <v>2478</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="5">
         <v>1844</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="5">
         <v>1221</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="5">
         <v>283</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="5">
         <v>5548</v>
       </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
+      <c r="G133" s="5">
+        <v>0</v>
+      </c>
+      <c r="H133" s="6">
         <v>29.2</v>
       </c>
-      <c r="I133">
+      <c r="I133" s="6">
         <v>0.5</v>
       </c>
-      <c r="J133">
+      <c r="J133" s="5">
         <v>8</v>
       </c>
-      <c r="K133">
+      <c r="K133" s="5">
         <v>5508</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
-      <c r="A134" s="2">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
+      <c r="A134" s="4">
         <v>45812</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="5">
         <v>2331</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="5">
         <v>1624</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="5">
         <v>1217</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="5">
         <v>279</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="5">
         <v>5508</v>
       </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
+      <c r="G134" s="5">
+        <v>0</v>
+      </c>
+      <c r="H134" s="6">
         <v>29.2</v>
       </c>
-      <c r="I134">
+      <c r="I134" s="6">
         <v>4.8</v>
       </c>
-      <c r="J134">
+      <c r="J134" s="5">
         <v>9</v>
       </c>
-      <c r="K134">
+      <c r="K134" s="5">
         <v>5499</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
-      <c r="A135" s="2">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
+      <c r="A135" s="4">
         <v>45813</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="5">
         <v>2231</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="5">
         <v>1590</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="5">
         <v>1200</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="5">
         <v>277</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="5">
         <v>5499</v>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
+      <c r="G135" s="5">
+        <v>0</v>
+      </c>
+      <c r="H135" s="6">
         <v>30.6</v>
       </c>
-      <c r="I135">
+      <c r="I135" s="6">
         <v>0.3</v>
       </c>
-      <c r="J135">
+      <c r="J135" s="6">
         <v>6.8</v>
       </c>
-      <c r="K135">
+      <c r="K135" s="5">
         <v>6169</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
-      <c r="A136" s="2">
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
+      <c r="A136" s="4">
         <v>45814</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="5">
         <v>2231</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="5">
         <v>1590</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="5">
         <v>1200</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="5">
         <v>277</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="5">
         <v>6169</v>
       </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
+      <c r="G136" s="5">
+        <v>0</v>
+      </c>
+      <c r="H136" s="6">
         <v>32.8</v>
       </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
+      <c r="I136" s="5">
+        <v>0</v>
+      </c>
+      <c r="J136" s="6">
         <v>5.3</v>
       </c>
-      <c r="K136">
+      <c r="K136" s="5">
         <v>6634</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
-      <c r="A137" s="2">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
+      <c r="A137" s="4">
         <v>45815</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="5">
         <v>2231</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="5">
         <v>1590</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="5">
         <v>1200</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="5">
         <v>277</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="5">
         <v>6634</v>
       </c>
-      <c r="G137">
+      <c r="G137" s="5">
         <v>1</v>
       </c>
-      <c r="H137">
+      <c r="H137" s="6">
         <v>34.6</v>
       </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
+      <c r="I137" s="5">
+        <v>0</v>
+      </c>
+      <c r="J137" s="6">
         <v>6.8</v>
       </c>
-      <c r="K137">
+      <c r="K137" s="5">
         <v>7086</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
-      <c r="A138" s="2">
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
+      <c r="A138" s="4">
         <v>45816</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="5">
         <v>2231</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="5">
         <v>1590</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="5">
         <v>1200</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="5">
         <v>277</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="5">
         <v>7086</v>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
+      <c r="G138" s="5">
+        <v>0</v>
+      </c>
+      <c r="H138" s="6">
         <v>36.7</v>
       </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
+      <c r="I138" s="5">
+        <v>0</v>
+      </c>
+      <c r="J138" s="6">
         <v>7.6</v>
       </c>
-      <c r="K138">
+      <c r="K138" s="5">
         <v>7388</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
-      <c r="A139" s="2">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
+      <c r="A139" s="4">
         <v>45817</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="5">
         <v>2231</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="5">
         <v>1590</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="5">
         <v>1200</v>
       </c>
-      <c r="E139">
+      <c r="E139" s="5">
         <v>277</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="5">
         <v>7388</v>
       </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
+      <c r="G139" s="5">
+        <v>0</v>
+      </c>
+      <c r="H139" s="6">
         <v>37.4</v>
       </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
+      <c r="I139" s="5">
+        <v>0</v>
+      </c>
+      <c r="J139" s="6">
         <v>10.8</v>
       </c>
-      <c r="K139">
+      <c r="K139" s="5">
         <v>7245</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
-      <c r="A140" s="2">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
+      <c r="A140" s="4">
         <v>45818</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="5">
         <v>3147</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="5">
         <v>2140</v>
       </c>
-      <c r="D140">
+      <c r="D140" s="5">
         <v>1645</v>
       </c>
-      <c r="E140">
+      <c r="E140" s="5">
         <v>336</v>
       </c>
-      <c r="F140">
+      <c r="F140" s="5">
         <v>7245</v>
       </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
+      <c r="G140" s="5">
+        <v>0</v>
+      </c>
+      <c r="H140" s="6">
         <v>37.3</v>
       </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
+      <c r="I140" s="5">
+        <v>0</v>
+      </c>
+      <c r="J140" s="6">
         <v>10.3</v>
       </c>
-      <c r="K140">
+      <c r="K140" s="5">
         <v>8231</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
-      <c r="A141" s="2">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
+      <c r="A141" s="4">
         <v>45819</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="5">
         <v>3749</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="5">
         <v>2359</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="5">
         <v>1834</v>
       </c>
-      <c r="E141">
+      <c r="E141" s="5">
         <v>361</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="5">
         <v>8231</v>
       </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
+      <c r="G141" s="5">
+        <v>0</v>
+      </c>
+      <c r="H141" s="6">
         <v>37.8</v>
       </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
+      <c r="I141" s="5">
+        <v>0</v>
+      </c>
+      <c r="J141" s="6">
         <v>10.8</v>
       </c>
-      <c r="K141">
+      <c r="K141" s="5">
         <v>8442</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
-      <c r="A142" s="2">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
+      <c r="A142" s="4">
         <v>45820</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="5">
         <v>3978</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="5">
         <v>2397</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="5">
         <v>1832</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="5">
         <v>384</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="5">
         <v>8442</v>
       </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-      <c r="H142">
+      <c r="G142" s="5">
+        <v>0</v>
+      </c>
+      <c r="H142" s="5">
         <v>37</v>
       </c>
-      <c r="I142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K142">
+      <c r="I142" s="5">
+        <v>0</v>
+      </c>
+      <c r="J142" s="6">
+        <v>9.8</v>
+      </c>
+      <c r="K142" s="5">
         <v>8438</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
-      <c r="A143" s="2">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
+      <c r="A143" s="4">
         <v>45821</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="5">
         <v>3822</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="5">
         <v>2698</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="5">
         <v>1822</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="5">
         <v>419</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="5">
         <v>8438</v>
       </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
+      <c r="G143" s="5">
+        <v>0</v>
+      </c>
+      <c r="H143" s="6">
         <v>35.4</v>
       </c>
-      <c r="I143">
+      <c r="I143" s="6">
         <v>0.1</v>
       </c>
-      <c r="J143">
+      <c r="J143" s="5">
         <v>14</v>
       </c>
-      <c r="K143">
+      <c r="K143" s="5">
         <v>7966</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
-      <c r="A144" s="2">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
+      <c r="A144" s="4">
         <v>45822</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="5">
         <v>3656</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="5">
         <v>2220</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="5">
         <v>1826</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="5">
         <v>359</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="5">
         <v>7966</v>
       </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
+      <c r="G144" s="5">
+        <v>0</v>
+      </c>
+      <c r="H144" s="5">
         <v>36</v>
       </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K144">
+      <c r="I144" s="5">
+        <v>0</v>
+      </c>
+      <c r="J144" s="6">
+        <v>9.8</v>
+      </c>
+      <c r="K144" s="5">
         <v>7829</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
-      <c r="A145" s="2">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
+      <c r="A145" s="4">
         <v>45823</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="5">
         <v>3585</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="5">
         <v>2175</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="5">
         <v>1756</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="5">
         <v>263</v>
       </c>
-      <c r="F145">
+      <c r="F145" s="5">
         <v>7829</v>
       </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
+      <c r="G145" s="5">
+        <v>0</v>
+      </c>
+      <c r="H145" s="6">
         <v>32.3</v>
       </c>
-      <c r="I145">
+      <c r="I145" s="6">
         <v>1.2</v>
       </c>
-      <c r="J145">
+      <c r="J145" s="6">
         <v>13.1</v>
       </c>
-      <c r="K145">
+      <c r="K145" s="5">
         <v>7179</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
-      <c r="A146" s="2">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
+      <c r="A146" s="4">
         <v>45824</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="5">
         <v>3229</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="5">
         <v>2018</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="5">
         <v>1640</v>
       </c>
-      <c r="E146">
+      <c r="E146" s="5">
         <v>394</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="5">
         <v>7179</v>
       </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
+      <c r="G146" s="5">
+        <v>0</v>
+      </c>
+      <c r="H146" s="6">
         <v>31.5</v>
       </c>
-      <c r="I146">
+      <c r="I146" s="6">
         <v>3.2</v>
       </c>
-      <c r="J146">
+      <c r="J146" s="6">
         <v>9.4</v>
       </c>
-      <c r="K146">
+      <c r="K146" s="5">
         <v>7057</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
-      <c r="A147" s="2">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
+      <c r="A147" s="4">
         <v>45825</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="5">
         <v>3130</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="5">
         <v>2308</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="5">
         <v>1560</v>
       </c>
-      <c r="E147">
+      <c r="E147" s="5">
         <v>405</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="5">
         <v>7057</v>
       </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
+      <c r="G147" s="5">
+        <v>0</v>
+      </c>
+      <c r="H147" s="6">
         <v>28.3</v>
       </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K147">
+      <c r="I147" s="5">
+        <v>0</v>
+      </c>
+      <c r="J147" s="6">
+        <v>8.3</v>
+      </c>
+      <c r="K147" s="5">
         <v>6517</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
-      <c r="A148" s="2">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
+      <c r="A148" s="4">
         <v>45826</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="5">
         <v>2928</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="5">
         <v>1998</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="5">
         <v>1490</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="5">
         <v>383</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="5">
         <v>6517</v>
       </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
+      <c r="G148" s="5">
+        <v>0</v>
+      </c>
+      <c r="H148" s="6">
         <v>30.2</v>
       </c>
-      <c r="I148">
+      <c r="I148" s="6">
         <v>40.9</v>
       </c>
-      <c r="J148">
+      <c r="J148" s="6">
         <v>6.1</v>
       </c>
-      <c r="K148">
+      <c r="K148" s="5">
         <v>6941</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
-      <c r="A149" s="2">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
+      <c r="A149" s="4">
         <v>45827</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="5">
         <v>3071</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="5">
         <v>2511</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="5">
         <v>1744</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="5">
         <v>382</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="5">
         <v>6941</v>
       </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
+      <c r="G149" s="5">
+        <v>0</v>
+      </c>
+      <c r="H149" s="5">
         <v>31</v>
       </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K149">
+      <c r="I149" s="5">
+        <v>0</v>
+      </c>
+      <c r="J149" s="6">
+        <v>9.8</v>
+      </c>
+      <c r="K149" s="5">
         <v>6780</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
-      <c r="A150" s="2">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
+      <c r="A150" s="4">
         <v>45828</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="5">
         <v>3029</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="5">
         <v>1994</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="5">
         <v>1533</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="5">
         <v>360</v>
       </c>
-      <c r="F150">
+      <c r="F150" s="5">
         <v>6780</v>
       </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150">
+      <c r="G150" s="5">
+        <v>0</v>
+      </c>
+      <c r="H150" s="6">
         <v>30.3</v>
       </c>
-      <c r="I150">
+      <c r="I150" s="6">
         <v>3.5</v>
       </c>
-      <c r="J150">
+      <c r="J150" s="6">
         <v>10.9</v>
       </c>
-      <c r="K150">
+      <c r="K150" s="5">
         <v>7001</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
-      <c r="A151" s="2">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
+      <c r="A151" s="4">
         <v>45829</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="5">
         <v>3115</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="5">
         <v>2248</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="5">
         <v>1688</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="5">
         <v>307</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="5">
         <v>7001</v>
       </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151">
+      <c r="G151" s="5">
+        <v>0</v>
+      </c>
+      <c r="H151" s="6">
         <v>31.9</v>
       </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151">
+      <c r="I151" s="5">
+        <v>0</v>
+      </c>
+      <c r="J151" s="6">
         <v>9.1</v>
       </c>
-      <c r="K151">
+      <c r="K151" s="5">
         <v>6863</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
-      <c r="A152" s="2">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
+      <c r="A152" s="4">
         <v>45830</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="5">
         <v>3038</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="5">
         <v>1964</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="5">
         <v>1591</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="5">
         <v>235</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="5">
         <v>6863</v>
       </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
+      <c r="G152" s="5">
+        <v>0</v>
+      </c>
+      <c r="H152" s="6">
         <v>31.6</v>
       </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
+      <c r="I152" s="5">
+        <v>0</v>
+      </c>
+      <c r="J152" s="6">
         <v>7.3</v>
       </c>
-      <c r="K152">
+      <c r="K152" s="5">
         <v>7177</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
-      <c r="A153" s="2">
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
+      <c r="A153" s="4">
         <v>45832</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="5">
         <v>3260</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="5">
         <v>2104</v>
       </c>
-      <c r="D153">
+      <c r="D153" s="5">
         <v>1587</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="5">
         <v>381</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="5">
         <v>7177</v>
       </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153">
+      <c r="G153" s="5">
+        <v>0</v>
+      </c>
+      <c r="H153" s="6">
         <v>31.4</v>
       </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
-      <c r="J153">
+      <c r="I153" s="5">
+        <v>0</v>
+      </c>
+      <c r="J153" s="5">
         <v>8</v>
       </c>
-      <c r="K153">
+      <c r="K153" s="5">
         <v>7104</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
-      <c r="A154" s="2">
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
+      <c r="A154" s="4">
         <v>45833</v>
       </c>
-      <c r="B154">
+      <c r="B154" s="5">
         <v>3213</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="5">
         <v>2023</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="5">
         <v>1595</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="5">
         <v>373</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="5">
         <v>7104</v>
       </c>
-      <c r="G154">
-        <v>0</v>
-      </c>
-      <c r="H154">
+      <c r="G154" s="5">
+        <v>0</v>
+      </c>
+      <c r="H154" s="6">
         <v>31.3</v>
       </c>
-      <c r="I154">
+      <c r="I154" s="6">
         <v>25.3</v>
       </c>
-      <c r="J154">
+      <c r="J154" s="6">
         <v>11.3</v>
       </c>
-      <c r="K154">
+      <c r="K154" s="5">
         <v>7460</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
-      <c r="A155" s="2">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
+      <c r="A155" s="4">
         <v>45834</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="5">
         <v>3274</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="5">
         <v>2181</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="5">
         <v>1751</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="5">
         <v>367</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="5">
         <v>7460</v>
       </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-      <c r="H155">
+      <c r="G155" s="5">
+        <v>0</v>
+      </c>
+      <c r="H155" s="6">
         <v>32.9</v>
       </c>
-      <c r="I155">
+      <c r="I155" s="6">
         <v>6.8</v>
       </c>
-      <c r="J155">
+      <c r="J155" s="6">
         <v>13.5</v>
       </c>
-      <c r="K155">
+      <c r="K155" s="5">
         <v>7632</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
-      <c r="A156" s="2">
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
+      <c r="A156" s="4">
         <v>45836</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="5">
         <v>3375</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="5">
         <v>2114</v>
       </c>
-      <c r="D156">
+      <c r="D156" s="5">
         <v>1733</v>
       </c>
-      <c r="E156">
+      <c r="E156" s="5">
         <v>326</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="5">
         <v>7473</v>
       </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-      <c r="H156">
+      <c r="G156" s="5">
+        <v>0</v>
+      </c>
+      <c r="H156" s="6">
         <v>30.5</v>
       </c>
-      <c r="I156">
+      <c r="I156" s="5">
         <v>2</v>
       </c>
-      <c r="J156">
+      <c r="J156" s="6">
         <v>7.6</v>
       </c>
-      <c r="K156">
+      <c r="K156" s="5">
         <v>6470</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
-      <c r="A157" s="2">
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
+      <c r="A157" s="4">
         <v>45837</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="5">
         <v>2857</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="5">
         <v>1836</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="5">
         <v>1507</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="5">
         <v>213</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="5">
         <v>6470</v>
       </c>
-      <c r="G157">
-        <v>0</v>
-      </c>
-      <c r="H157">
+      <c r="G157" s="5">
+        <v>0</v>
+      </c>
+      <c r="H157" s="6">
         <v>28.3</v>
       </c>
-      <c r="I157">
+      <c r="I157" s="5">
         <v>3</v>
       </c>
-      <c r="J157">
+      <c r="J157" s="6">
         <v>7.9</v>
       </c>
-      <c r="K157">
+      <c r="K157" s="5">
         <v>5897</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
-      <c r="A158" s="2">
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
+      <c r="A158" s="4">
         <v>45838</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="5">
         <v>2632</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="5">
         <v>2006</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="5">
         <v>1289</v>
       </c>
-      <c r="E158">
+      <c r="E158" s="5">
         <v>313</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="5">
         <v>5897</v>
       </c>
-      <c r="G158">
-        <v>0</v>
-      </c>
-      <c r="H158">
+      <c r="G158" s="5">
+        <v>0</v>
+      </c>
+      <c r="H158" s="6">
         <v>27.6</v>
       </c>
-      <c r="I158">
+      <c r="I158" s="6">
         <v>34.2</v>
       </c>
-      <c r="J158">
+      <c r="J158" s="6">
         <v>7.2</v>
       </c>
-      <c r="K158">
+      <c r="K158" s="5">
         <v>6506</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
-      <c r="A159" s="2">
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
+      <c r="A159" s="4">
         <v>45839</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="5">
         <v>2918</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="5">
         <v>2088</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="5">
         <v>1456</v>
       </c>
-      <c r="E159">
+      <c r="E159" s="5">
         <v>352</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="5">
         <v>6506</v>
       </c>
-      <c r="G159">
-        <v>0</v>
-      </c>
-      <c r="H159">
+      <c r="G159" s="5">
+        <v>0</v>
+      </c>
+      <c r="H159" s="6">
         <v>29.5</v>
       </c>
-      <c r="I159">
+      <c r="I159" s="6">
         <v>2.3</v>
       </c>
-      <c r="J159">
+      <c r="J159" s="6">
         <v>7.6</v>
       </c>
-      <c r="K159">
+      <c r="K159" s="5">
         <v>7178</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
-      <c r="A160" s="2">
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
+      <c r="A160" s="4">
         <v>45840</v>
       </c>
-      <c r="B160">
+      <c r="B160" s="5">
         <v>3229</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="5">
         <v>2120</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="5">
         <v>1623</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="5">
         <v>337</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="5">
         <v>7178</v>
       </c>
-      <c r="G160">
-        <v>0</v>
-      </c>
-      <c r="H160">
+      <c r="G160" s="5">
+        <v>0</v>
+      </c>
+      <c r="H160" s="6">
         <v>31.4</v>
       </c>
-      <c r="I160">
+      <c r="I160" s="6">
         <v>0.3</v>
       </c>
-      <c r="J160">
+      <c r="J160" s="6">
         <v>10.2</v>
       </c>
-      <c r="K160">
+      <c r="K160" s="5">
         <v>7410</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
-      <c r="A161" s="2">
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
+      <c r="A161" s="4">
         <v>45841</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="5">
         <v>3368</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="5">
         <v>2507</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="5">
         <v>1750</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="5">
         <v>327</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="5">
         <v>7410</v>
       </c>
-      <c r="G161">
-        <v>0</v>
-      </c>
-      <c r="H161">
+      <c r="G161" s="5">
+        <v>0</v>
+      </c>
+      <c r="H161" s="6">
         <v>31.9</v>
       </c>
-      <c r="I161">
+      <c r="I161" s="6">
         <v>2.2</v>
       </c>
-      <c r="J161">
+      <c r="J161" s="6">
         <v>12.7</v>
       </c>
-      <c r="K161">
+      <c r="K161" s="5">
         <v>7166</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
-      <c r="A162" s="2">
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
+      <c r="A162" s="4">
         <v>45842</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="5">
         <v>3246</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="5">
         <v>2131</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="5">
         <v>1643</v>
       </c>
-      <c r="E162">
+      <c r="E162" s="5">
         <v>320</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="5">
         <v>7166</v>
       </c>
-      <c r="G162">
-        <v>0</v>
-      </c>
-      <c r="H162">
+      <c r="G162" s="5">
+        <v>0</v>
+      </c>
+      <c r="H162" s="6">
         <v>30.2</v>
       </c>
-      <c r="I162">
-        <v>0</v>
-      </c>
-      <c r="J162">
+      <c r="I162" s="5">
+        <v>0</v>
+      </c>
+      <c r="J162" s="6">
         <v>7.6</v>
       </c>
-      <c r="K162">
+      <c r="K162" s="5">
         <v>7170</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
-      <c r="A163" s="2">
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
+      <c r="A163" s="4">
         <v>45843</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="5">
         <v>3303</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="5">
         <v>2015</v>
       </c>
-      <c r="D163">
+      <c r="D163" s="5">
         <v>1660</v>
       </c>
-      <c r="E163">
+      <c r="E163" s="5">
         <v>306</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="5">
         <v>7170</v>
       </c>
-      <c r="G163">
-        <v>0</v>
-      </c>
-      <c r="H163">
+      <c r="G163" s="5">
+        <v>0</v>
+      </c>
+      <c r="H163" s="6">
         <v>31.4</v>
       </c>
-      <c r="I163">
+      <c r="I163" s="6">
         <v>5.1</v>
       </c>
-      <c r="J163">
+      <c r="J163" s="6">
         <v>5.5</v>
       </c>
-      <c r="K163">
+      <c r="K163" s="5">
         <v>7148</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
-      <c r="A164" s="2">
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
+      <c r="A164" s="4">
         <v>45844</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="5">
         <v>3236</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="5">
         <v>1989</v>
       </c>
-      <c r="D164">
+      <c r="D164" s="5">
         <v>1628</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="5">
         <v>255</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="5">
         <v>7148</v>
       </c>
-      <c r="G164">
+      <c r="G164" s="5">
         <v>1</v>
       </c>
-      <c r="H164">
+      <c r="H164" s="6">
         <v>30.2</v>
       </c>
-      <c r="I164">
+      <c r="I164" s="6">
         <v>21.1</v>
       </c>
-      <c r="J164">
+      <c r="J164" s="6">
         <v>6.5</v>
       </c>
-      <c r="K164">
+      <c r="K164" s="5">
         <v>6875</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
-      <c r="A165" s="2">
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
+      <c r="A165" s="4">
         <v>45845</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="5">
         <v>3069</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="5">
         <v>2250</v>
       </c>
-      <c r="D165">
+      <c r="D165" s="5">
         <v>1581</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="5">
         <v>373</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="5">
         <v>6875</v>
       </c>
-      <c r="G165">
-        <v>0</v>
-      </c>
-      <c r="H165">
+      <c r="G165" s="5">
+        <v>0</v>
+      </c>
+      <c r="H165" s="6">
         <v>29.1</v>
       </c>
-      <c r="I165">
+      <c r="I165" s="6">
         <v>21.1</v>
       </c>
-      <c r="J165">
+      <c r="J165" s="6">
         <v>9.1</v>
       </c>
-      <c r="K165">
+      <c r="K165" s="5">
         <v>7536</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
-      <c r="A166" s="2">
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
+      <c r="A166" s="4">
         <v>45847</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="5">
         <v>3096</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="5">
         <v>2133</v>
       </c>
-      <c r="D166">
+      <c r="D166" s="5">
         <v>1643</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="5">
         <v>382</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="5">
         <v>7203</v>
       </c>
-      <c r="G166">
-        <v>0</v>
-      </c>
-      <c r="H166">
+      <c r="G166" s="5">
+        <v>0</v>
+      </c>
+      <c r="H166" s="6">
         <v>28.6</v>
       </c>
-      <c r="I166">
+      <c r="I166" s="6">
         <v>0.3</v>
       </c>
-      <c r="J166">
+      <c r="J166" s="6">
         <v>7.5</v>
       </c>
-      <c r="K166">
+      <c r="K166" s="5">
         <v>5973</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
-      <c r="A167" s="2">
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
+      <c r="A167" s="4">
         <v>45848</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="5">
         <v>2615</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="5">
         <v>1909</v>
       </c>
-      <c r="D167">
+      <c r="D167" s="5">
         <v>1379</v>
       </c>
-      <c r="E167">
+      <c r="E167" s="5">
         <v>352</v>
       </c>
-      <c r="F167">
+      <c r="F167" s="5">
         <v>5973</v>
       </c>
-      <c r="G167">
-        <v>0</v>
-      </c>
-      <c r="H167">
+      <c r="G167" s="5">
+        <v>0</v>
+      </c>
+      <c r="H167" s="6">
         <v>27.2</v>
       </c>
-      <c r="I167">
+      <c r="I167" s="6">
         <v>59.9</v>
       </c>
-      <c r="J167">
+      <c r="J167" s="6">
         <v>7.5</v>
       </c>
-      <c r="K167">
+      <c r="K167" s="5">
         <v>6233</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
-      <c r="A168" s="2">
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
+      <c r="A168" s="4">
         <v>45849</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="5">
         <v>2712</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="5">
         <v>2028</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="5">
         <v>1408</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="5">
         <v>360</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="5">
         <v>6233</v>
       </c>
-      <c r="G168">
-        <v>0</v>
-      </c>
-      <c r="H168">
+      <c r="G168" s="5">
+        <v>0</v>
+      </c>
+      <c r="H168" s="6">
         <v>28.9</v>
       </c>
-      <c r="I168">
+      <c r="I168" s="5">
         <v>18</v>
       </c>
-      <c r="J168">
+      <c r="J168" s="6">
         <v>4.6</v>
       </c>
-      <c r="K168">
+      <c r="K168" s="5">
         <v>6275</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
-      <c r="A169" s="2">
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
+      <c r="A169" s="4">
         <v>45850</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="5">
         <v>2735</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="5">
         <v>1874</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="5">
         <v>1478</v>
       </c>
-      <c r="E169">
+      <c r="E169" s="5">
         <v>305</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="5">
         <v>6275</v>
       </c>
-      <c r="G169">
-        <v>0</v>
-      </c>
-      <c r="H169">
+      <c r="G169" s="5">
+        <v>0</v>
+      </c>
+      <c r="H169" s="6">
         <v>29.4</v>
       </c>
-      <c r="I169">
+      <c r="I169" s="6">
         <v>7.9</v>
       </c>
-      <c r="J169">
+      <c r="J169" s="6">
         <v>7.9</v>
       </c>
-      <c r="K169">
+      <c r="K169" s="5">
         <v>5733</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
-      <c r="A170" s="2">
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
+      <c r="A170" s="4">
         <v>45851</v>
       </c>
-      <c r="B170">
+      <c r="B170" s="5">
         <v>2601</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="5">
         <v>1691</v>
       </c>
-      <c r="D170">
+      <c r="D170" s="5">
         <v>1329</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="5">
         <v>290</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="5">
         <v>5733</v>
       </c>
-      <c r="G170">
-        <v>0</v>
-      </c>
-      <c r="H170">
+      <c r="G170" s="5">
+        <v>0</v>
+      </c>
+      <c r="H170" s="6">
         <v>29.3</v>
       </c>
-      <c r="I170">
+      <c r="I170" s="6">
         <v>0.5</v>
       </c>
-      <c r="J170">
+      <c r="J170" s="6">
         <v>7.2</v>
       </c>
-      <c r="K170">
+      <c r="K170" s="5">
         <v>6197</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
-      <c r="A171" s="2">
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
+      <c r="A171" s="4">
         <v>45852</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="5">
         <v>2643</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="5">
         <v>2135</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="5">
         <v>1375</v>
       </c>
-      <c r="E171">
+      <c r="E171" s="5">
         <v>366</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="5">
         <v>6197</v>
       </c>
-      <c r="G171">
-        <v>0</v>
-      </c>
-      <c r="H171">
+      <c r="G171" s="5">
+        <v>0</v>
+      </c>
+      <c r="H171" s="6">
         <v>28.1</v>
       </c>
-      <c r="I171">
+      <c r="I171" s="6">
         <v>4.3</v>
       </c>
-      <c r="J171">
+      <c r="J171" s="6">
         <v>10.7</v>
       </c>
-      <c r="K171">
+      <c r="K171" s="5">
         <v>6397</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
-      <c r="A172" s="2">
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
+      <c r="A172" s="4">
         <v>45854</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="5">
         <v>2752</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="5">
         <v>1914</v>
       </c>
-      <c r="D172">
+      <c r="D172" s="5">
         <v>1445</v>
       </c>
-      <c r="E172">
+      <c r="E172" s="5">
         <v>391</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="5">
         <v>6397</v>
       </c>
-      <c r="G172">
-        <v>0</v>
-      </c>
-      <c r="H172">
+      <c r="G172" s="5">
+        <v>0</v>
+      </c>
+      <c r="H172" s="6">
         <v>29.7</v>
       </c>
-      <c r="I172">
+      <c r="I172" s="6">
         <v>4.5</v>
       </c>
-      <c r="J172">
+      <c r="J172" s="6">
         <v>11.4</v>
       </c>
-      <c r="K172">
+      <c r="K172" s="5">
         <v>6324</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
-      <c r="A173" s="2">
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
+      <c r="A173" s="4">
         <v>45855</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="5">
         <v>2643</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="5">
         <v>2021</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="5">
         <v>1450</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="5">
         <v>349</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="5">
         <v>6324</v>
       </c>
-      <c r="G173">
-        <v>0</v>
-      </c>
-      <c r="H173">
+      <c r="G173" s="5">
+        <v>0</v>
+      </c>
+      <c r="H173" s="6">
         <v>28.8</v>
       </c>
-      <c r="I173">
+      <c r="I173" s="6">
         <v>5.1</v>
       </c>
-      <c r="J173">
+      <c r="J173" s="6">
         <v>8.6</v>
       </c>
-      <c r="K173">
+      <c r="K173" s="5">
         <v>6197</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
-      <c r="A174" s="2">
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
+      <c r="A174" s="4">
         <v>45856</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="5">
         <v>2435</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="5">
         <v>1660</v>
       </c>
-      <c r="D174">
+      <c r="D174" s="5">
         <v>1289</v>
       </c>
-      <c r="E174">
+      <c r="E174" s="5">
         <v>187</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="5">
         <v>6197</v>
       </c>
-      <c r="G174">
-        <v>0</v>
-      </c>
-      <c r="H174">
+      <c r="G174" s="5">
+        <v>0</v>
+      </c>
+      <c r="H174" s="6">
         <v>30.1</v>
       </c>
-      <c r="I174">
+      <c r="I174" s="6">
         <v>3.3</v>
       </c>
-      <c r="J174">
+      <c r="J174" s="5">
         <v>9</v>
       </c>
-      <c r="K174">
+      <c r="K174" s="5">
         <v>5707</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
-      <c r="A175" s="2">
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
+      <c r="A175" s="4">
         <v>45857</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="5">
         <v>2470</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="5">
         <v>1661</v>
       </c>
-      <c r="D175">
+      <c r="D175" s="5">
         <v>1285</v>
       </c>
-      <c r="E175">
+      <c r="E175" s="5">
         <v>177</v>
       </c>
-      <c r="F175">
-        <v>5707</v>
-      </c>
-      <c r="G175">
-        <v>0</v>
-      </c>
-      <c r="H175">
+      <c r="F175" s="5">
+        <v>5958</v>
+      </c>
+      <c r="G175" s="5">
+        <v>0</v>
+      </c>
+      <c r="H175" s="6">
         <v>30.7</v>
       </c>
-      <c r="I175">
-        <v>0</v>
-      </c>
-      <c r="J175">
+      <c r="I175" s="5">
+        <v>0</v>
+      </c>
+      <c r="J175" s="5">
         <v>8</v>
       </c>
+      <c r="K175" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
